--- a/ipo_data_scrap/ipo_data.xlsx
+++ b/ipo_data_scrap/ipo_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,74 +523,74 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Indogulfropsciences IPO</t>
+          <t>rizac IPO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹11 (9.91%)</t>
+          <t>₹-- (0.00%)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.91</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>111</v>
+        <v>245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>122 (9.91%)</t>
+          <t>245 (0%)</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>9.91</v>
+        <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>₹200.00r</t>
+          <t>₹860.00r</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>26-Jun</t>
+          <t>2-Jul</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>30-Jun</t>
+          <t>4-Jul</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>1-Jul</t>
+          <t>7-Jul</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>3-Jul</t>
+          <t>9-Jul</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>23-Jun 17:55</t>
+          <t>27-Jun 10:30</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>1299</v>
+        <v>1308</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -601,74 +601,78 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDB Financial IPO</t>
+          <t>Indogulfropsciences IPO O</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹74 (10.00%)</t>
+          <t>₹9 (8.11%)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>740</v>
+        <v>111</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>814 (10%)</t>
+          <t>120 (8.11%)</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>₹12500.00r</t>
+          <t>₹200.00r</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>135</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>25-Jun</t>
+          <t>26-Jun</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>27-Jun</t>
+          <t>30-Jun</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>30-Jun</t>
+          <t>1-Jul</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2-Jul</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
+          <t>3-Jul</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.54x</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>23-Jun 17:59</t>
+          <t>27-Jun 10:28</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>1276</v>
+        <v>1299</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -679,30 +683,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sambhv Steel Tubes IPO</t>
+          <t>Sambhv Steel Tubes IPOT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹8 (9.76%)</t>
+          <t>₹12 (14.63%)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9.76</v>
+        <v>14.63</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
         <v>82</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>90 (9.76%)</t>
+          <t>94 (14.63%)</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>9.76</v>
+        <v>14.63</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -739,10 +743,14 @@
           <t>2-Jul</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>1.81x</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>23-Jun 17:58</t>
+          <t>27-Jun 10:31</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -757,74 +765,78 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kalpataru IPO</t>
+          <t>HDB Financial IPOT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹9 (2.17%)</t>
+          <t>₹53 (7.16%)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2.17</v>
+        <v>7.16</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>414</v>
+        <v>740</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>423 (2.17%)</t>
+          <t>793 (7.16%)</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2.17</v>
+        <v>7.16</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>₹1590.00r</t>
+          <t>₹12500.00r</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-59.52</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>24-Jun</t>
+          <t>25-Jun</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>26-Jun</t>
+          <t>27-Jun</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>27-Jun</t>
+          <t>30-Jun</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1-Jul</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
+          <t>2-Jul</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>1.67x</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>23-Jun 18:00</t>
+          <t>27-Jun 10:35</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -835,44 +847,44 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ellenbarrie Industrial Gases IPO</t>
+          <t>Kalpataru IPO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹10 (2.50%)</t>
+          <t>₹3 (0.72%)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2.5</v>
+        <v>0.72</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>410 (2.5%)</t>
+          <t>417 (0.72%)</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2.5</v>
+        <v>0.72</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>₹852.53r</t>
+          <t>₹1590.00r</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>62.88</t>
+          <t>-59.52</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -895,14 +907,18 @@
           <t>1-Jul</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2.31x</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>23-Jun 18:02</t>
+          <t>27-Jun 10:37</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -913,44 +929,44 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Globeivil Projects IPO</t>
+          <t>Ellenbarrie Industrial Gases IPO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>₹15 (21.13%)</t>
+          <t>₹41 (10.25%)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.13</v>
+        <v>10.25</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>71</v>
+        <v>400</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>86 (21.13%)</t>
+          <t>441 (10.25%)</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>21.13</v>
+        <v>10.25</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>₹119.00r</t>
+          <t>₹852.53r</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>62.88</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -973,14 +989,18 @@
           <t>1-Jul</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>17.37x</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>23-Jun 17:59</t>
+          <t>27-Jun 10:32</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -991,78 +1011,78 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Arisinfra Solutions IPO</t>
+          <t>Globeivil Projects IPO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>₹-- (0.00%)</t>
+          <t>₹21 (29.58%)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>29.58</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>222</v>
+        <v>71</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>222 (0%)</t>
+          <t>92 (29.58%)</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>29.58</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>₹499.60r</t>
+          <t>₹119.00r</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>211</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-41.89</t>
+          <t>19.83</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>18-Jun</t>
+          <t>24-Jun</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>20-Jun</t>
+          <t>26-Jun</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>23-Jun</t>
+          <t>27-Jun</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>25-Jun</t>
+          <t>1-Jul</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2.8x</t>
+          <t>80.97x</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>23-Jun 17:58</t>
+          <t>27-Jun 10:31</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>1275</v>
+        <v>1280</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1073,78 +1093,78 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Oswal Pumps IPO</t>
+          <t>Arisinfra Solutions IPO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>₹41 (6.68%)</t>
+          <t>₹-- (0.00%)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6.68</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>614</v>
+        <v>222</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>655 (6.68%)</t>
+          <t>222 (0%)</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>6.68</v>
+        <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>₹1387.34r</t>
+          <t>₹499.60r</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>67</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>62.54</t>
+          <t>-41.89</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>13-Jun</t>
+          <t>18-Jun</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>17-Jun</t>
+          <t>20-Jun</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>18-Jun</t>
+          <t>23-Jun</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>20-Jun</t>
+          <t>25-Jun</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>28.44x</t>
+          <t>2.8x</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>20-Jun 8:57</t>
+          <t>25-Jun 5:55</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>1268</v>
+        <v>1275</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
